--- a/SGC-CKN/Excel/39c28cbb-00a8-44eb-a165-a084a776f8e9_Cọc_khoan_nhồi_-_Trụ_HN478_C9_D2000_05-03-2026.xlsx
+++ b/SGC-CKN/Excel/39c28cbb-00a8-44eb-a165-a084a776f8e9_Cọc_khoan_nhồi_-_Trụ_HN478_C9_D2000_05-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="78">
   <si>
     <t>Dự án</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Tên bộ phận</t>
   </si>
   <si>
-    <t>Cọc khoan nhồi - Trụ HN478</t>
+    <t>Cọc khoan nhồi - Trụ HN P479</t>
   </si>
   <si>
     <t>Số hiệu cọc</t>
@@ -41,7 +41,7 @@
     <t>Biên bản số</t>
   </si>
   <si>
-    <t>ĐSTĐC/CKN05-HN478/06</t>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>10:20 04/03/2026</t>
+    <t>10:30 03/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>09:10 05/03/2026</t>
+    <t>16:30 04/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -95,154 +95,157 @@
     <t>1</t>
   </si>
   <si>
-    <t>Cát mịn màu xám lẫn bùn sét, mùn thực vật, kết cấu xốp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10h20
+    <t>Sét pha màu xám đen, trạng thái dẻo mềm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:30
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:57
+03/03/2026</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Sét màu xám ghi, trạng thái dẻo cứng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:26
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:55
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:25
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:58
+03/03/2026</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Cát xám ghi, kết cấu chặt vừa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:24
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:45
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:04
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:20
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:44
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:00
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:16
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:33
+03/03/2026</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét màu xám đen, trạng thái dẻo cứng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:57
+03/03/2026</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Cát, sạn, sỏi đa khoáng, đa sắc kết cấu chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:20
+03/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:08
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">10h45
+    <t>6</t>
+  </si>
+  <si>
+    <t>Cuội sỏi to, sạn cát đa khoáng, đa sắc, kết cấu rất chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:51
 04/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">11h05
+    <t xml:space="preserve">10:28
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">11h28
+    <t xml:space="preserve">11:02
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">12h00
+    <t xml:space="preserve">11:40
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">12h15
+    <t xml:space="preserve">12:09
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">12h37
+    <t xml:space="preserve">12:46
 04/03/2026</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Cát mịn xám đen, kết cấu chặt vừa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13h00
+    <t xml:space="preserve">13:12
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">13h18
+    <t xml:space="preserve">13:30
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">13h34
+    <t xml:space="preserve">14:15
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">13h58
+    <t xml:space="preserve">14:55
 04/03/2026</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét xám ghi, trạng thái dẻo cứng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14h19
+    <t xml:space="preserve">15:32
 04/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">14h45
+    <t xml:space="preserve">16:00
 04/03/2026</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Cát, sạn, sỏi nhỏ màu xám ghi, kết cấu chặt vừa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15h12
+    <t xml:space="preserve">16:30
 04/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15h36
-04/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16h05
-04/03/2026</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Sạn, sỏi, cuội cát đa sắc, đa khoáng, kết cấu chặt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16h29
-04/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16h47
-04/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00h16
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00h58
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01h27
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02h35
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03h02
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05h11
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05h52
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06h31
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07h10
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07h52
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08h37
-05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09h10
-05/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -279,7 +282,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -337,6 +340,17 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF365314"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -347,7 +361,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,11 +395,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
       </patternFill>
     </fill>
@@ -396,12 +405,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9F99D"/>
       </patternFill>
     </fill>
     <fill>
@@ -497,7 +521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -523,26 +547,26 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -562,13 +586,25 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -594,7 +630,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="8096250" cy="10477500"/>
@@ -954,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1154,407 +1190,407 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-9.52</v>
+        <v>-6.72</v>
       </c>
       <c r="G11" s="5">
-        <v>-10.38</v>
+        <v>-8.81</v>
       </c>
       <c r="H11" s="5">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="I11" s="5">
-        <v>0.86</v>
+        <v>2.09</v>
       </c>
       <c r="J11" s="8">
+        <v>4.64</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="9">
+        <v>-8.81</v>
+      </c>
+      <c r="G12" s="9">
+        <v>-10.88</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0.48</v>
+      </c>
+      <c r="I12" s="9">
+        <v>2.07</v>
+      </c>
+      <c r="J12" s="8">
+        <v>4.28</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="9">
+        <v>-10.88</v>
+      </c>
+      <c r="G13" s="9">
+        <v>-12.94</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="I13" s="9">
         <v>2.06</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="J13" s="8">
+        <v>4.12</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="B14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="5">
-        <v>-10.38</v>
-      </c>
-      <c r="G12" s="5">
-        <v>-11.7</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0.33</v>
-      </c>
-      <c r="I12" s="5">
-        <v>1.32</v>
-      </c>
-      <c r="J12" s="8">
-        <v>3.96</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="5">
-        <v>-11.7</v>
-      </c>
-      <c r="G13" s="5">
-        <v>-13.62</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="5">
-        <v>1.92</v>
-      </c>
-      <c r="J13" s="8">
-        <v>3.84</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="D14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="5">
-        <v>-13.62</v>
-      </c>
-      <c r="G14" s="5">
-        <v>-15.51</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="I14" s="5">
-        <v>1.89</v>
-      </c>
-      <c r="J14" s="9">
-        <v>7.56</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>30</v>
+      <c r="E14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="9">
+        <v>-12.94</v>
+      </c>
+      <c r="G14" s="9">
+        <v>-14.1</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0.55</v>
+      </c>
+      <c r="I14" s="9">
+        <v>1.16</v>
+      </c>
+      <c r="J14" s="8">
+        <v>2.11</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="A15" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="5">
-        <v>-15.51</v>
-      </c>
-      <c r="G15" s="5">
-        <v>-16.7</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0.37</v>
-      </c>
-      <c r="I15" s="5">
-        <v>1.19</v>
+      <c r="E15" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="12">
+        <v>-14.1</v>
+      </c>
+      <c r="G15" s="12">
+        <v>-16.14</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0.43</v>
+      </c>
+      <c r="I15" s="12">
+        <v>2.04</v>
       </c>
       <c r="J15" s="8">
-        <v>3.25</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>30</v>
+        <v>4.71</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="11" t="s">
+      <c r="B16" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="12" t="s">
+      <c r="D16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="10">
-        <v>-16.7</v>
-      </c>
-      <c r="G16" s="10">
-        <v>-18.3</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0.38</v>
-      </c>
-      <c r="I16" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="J16" s="8">
-        <v>4.17</v>
-      </c>
-      <c r="K16" s="11" t="s">
-        <v>30</v>
+      <c r="E16" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="12">
+        <v>-16.14</v>
+      </c>
+      <c r="G16" s="12">
+        <v>-18.22</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0.35</v>
+      </c>
+      <c r="I16" s="12">
+        <v>2.08</v>
+      </c>
+      <c r="J16" s="15">
+        <v>5.94</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="B17" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="12" t="s">
+      <c r="D17" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="10">
-        <v>-18.3</v>
-      </c>
-      <c r="G17" s="10">
-        <v>-20.41</v>
-      </c>
-      <c r="H17" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="I17" s="10">
+      <c r="E17" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="12">
+        <v>-18.22</v>
+      </c>
+      <c r="G17" s="12">
+        <v>-20.43</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0.32</v>
+      </c>
+      <c r="I17" s="12">
+        <v>2.21</v>
+      </c>
+      <c r="J17" s="15">
+        <v>6.98</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="12">
+        <v>-20.43</v>
+      </c>
+      <c r="G18" s="12">
+        <v>-22.56</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0.27</v>
+      </c>
+      <c r="I18" s="12">
+        <v>2.13</v>
+      </c>
+      <c r="J18" s="15">
+        <v>7.99</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="12">
+        <v>-22.56</v>
+      </c>
+      <c r="G19" s="12">
+        <v>-24.67</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="I19" s="12">
         <v>2.11</v>
       </c>
-      <c r="J17" s="9">
-        <v>7.03</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="J19" s="15">
+        <v>5.28</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="11" t="s">
+      <c r="B20" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="10">
-        <v>-20.41</v>
-      </c>
-      <c r="G18" s="10">
-        <v>-22.33</v>
-      </c>
-      <c r="H18" s="10">
+      <c r="D20" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="12">
+        <v>-24.67</v>
+      </c>
+      <c r="G20" s="12">
+        <v>-26.73</v>
+      </c>
+      <c r="H20" s="12">
         <v>0.27</v>
       </c>
-      <c r="I18" s="10">
-        <v>1.92</v>
-      </c>
-      <c r="J18" s="9">
-        <v>7.2</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="I20" s="12">
+        <v>2.06</v>
+      </c>
+      <c r="J20" s="15">
+        <v>7.72</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="11" t="s">
+      <c r="B21" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F19" s="10">
-        <v>-22.33</v>
-      </c>
-      <c r="G19" s="10">
-        <v>-24.6</v>
-      </c>
-      <c r="H19" s="10">
-        <v>0.4</v>
-      </c>
-      <c r="I19" s="10">
-        <v>2.27</v>
-      </c>
-      <c r="J19" s="9">
-        <v>5.68</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="14" t="s">
+      <c r="D21" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="15" t="s">
+      <c r="E21" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="13">
-        <v>-24.6</v>
-      </c>
-      <c r="G20" s="13">
-        <v>-26.9</v>
-      </c>
-      <c r="H20" s="13">
-        <v>0.35</v>
-      </c>
-      <c r="I20" s="13">
-        <v>2.3</v>
-      </c>
-      <c r="J20" s="9">
-        <v>6.57</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="15" t="s">
+      <c r="F21" s="12">
+        <v>-26.73</v>
+      </c>
+      <c r="G21" s="12">
+        <v>-28.87</v>
+      </c>
+      <c r="H21" s="12">
+        <v>0.27</v>
+      </c>
+      <c r="I21" s="12">
+        <v>2.14</v>
+      </c>
+      <c r="J21" s="15">
+        <v>8.03</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E22" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="13">
-        <v>-26.9</v>
-      </c>
-      <c r="G21" s="13">
-        <v>-28.7</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0.43</v>
-      </c>
-      <c r="I21" s="13">
-        <v>1.8</v>
-      </c>
-      <c r="J21" s="8">
-        <v>4.15</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="16">
-        <v>-28.7</v>
-      </c>
-      <c r="G22" s="16">
-        <v>-30.64</v>
-      </c>
-      <c r="H22" s="16">
-        <v>0.45</v>
-      </c>
-      <c r="I22" s="16">
-        <v>1.94</v>
-      </c>
-      <c r="J22" s="8">
-        <v>4.31</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>30</v>
+      <c r="F22" s="12">
+        <v>-28.87</v>
+      </c>
+      <c r="G22" s="12">
+        <v>-31.01</v>
+      </c>
+      <c r="H22" s="12">
+        <v>0.28</v>
+      </c>
+      <c r="I22" s="12">
+        <v>2.14</v>
+      </c>
+      <c r="J22" s="15">
+        <v>7.55</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1568,570 +1604,536 @@
         <v>47</v>
       </c>
       <c r="D23" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>49</v>
-      </c>
       <c r="F23" s="16">
-        <v>-30.64</v>
+        <v>-31.01</v>
       </c>
       <c r="G23" s="16">
-        <v>-32.68</v>
+        <v>-33.12</v>
       </c>
       <c r="H23" s="16">
         <v>0.4</v>
       </c>
       <c r="I23" s="16">
-        <v>2.04</v>
-      </c>
-      <c r="J23" s="9">
-        <v>5.1</v>
+        <v>2.11</v>
+      </c>
+      <c r="J23" s="15">
+        <v>5.27</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="18" t="s">
+      <c r="A24" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="B24" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="16">
-        <v>-32.68</v>
-      </c>
-      <c r="G24" s="16">
-        <v>-34.71</v>
-      </c>
-      <c r="H24" s="16">
-        <v>0.48</v>
-      </c>
-      <c r="I24" s="16">
-        <v>2.03</v>
-      </c>
-      <c r="J24" s="8">
-        <v>4.2</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>30</v>
+      <c r="D24" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="19">
+        <v>-33.12</v>
+      </c>
+      <c r="G24" s="19">
+        <v>-35.08</v>
+      </c>
+      <c r="H24" s="19">
+        <v>0.38</v>
+      </c>
+      <c r="I24" s="19">
+        <v>1.96</v>
+      </c>
+      <c r="J24" s="15">
+        <v>5.11</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="20" t="s">
+      <c r="E25" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="21" t="s">
+      <c r="F25" s="19">
+        <v>-35.08</v>
+      </c>
+      <c r="G25" s="19">
+        <v>-37.06</v>
+      </c>
+      <c r="H25" s="19">
+        <v>15.8</v>
+      </c>
+      <c r="I25" s="19">
+        <v>1.98</v>
+      </c>
+      <c r="J25" s="22">
+        <v>0.13</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="19">
-        <v>-34.71</v>
-      </c>
-      <c r="G25" s="19">
-        <v>-36.82</v>
-      </c>
-      <c r="H25" s="19">
-        <v>0.4</v>
-      </c>
-      <c r="I25" s="19">
-        <v>2.11</v>
-      </c>
-      <c r="J25" s="9">
-        <v>5.27</v>
-      </c>
-      <c r="K25" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="20" t="s">
+      <c r="B26" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="E26" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="23">
+        <v>-37.06</v>
+      </c>
+      <c r="G26" s="23">
+        <v>-39.12</v>
+      </c>
+      <c r="H26" s="23">
+        <v>0.72</v>
+      </c>
+      <c r="I26" s="23">
+        <v>2.06</v>
+      </c>
+      <c r="J26" s="8">
+        <v>2.87</v>
+      </c>
+      <c r="K26" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="B27" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="19">
-        <v>-36.82</v>
-      </c>
-      <c r="G26" s="19">
-        <v>-38.95</v>
-      </c>
-      <c r="H26" s="19">
+      <c r="D27" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="23">
+        <v>-39.12</v>
+      </c>
+      <c r="G27" s="23">
+        <v>-40.98</v>
+      </c>
+      <c r="H27" s="23">
+        <v>0.62</v>
+      </c>
+      <c r="I27" s="23">
+        <v>1.86</v>
+      </c>
+      <c r="J27" s="8">
+        <v>3.02</v>
+      </c>
+      <c r="K27" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="23">
+        <v>-40.98</v>
+      </c>
+      <c r="G28" s="23">
+        <v>-43.1</v>
+      </c>
+      <c r="H28" s="23">
+        <v>0.57</v>
+      </c>
+      <c r="I28" s="23">
+        <v>2.12</v>
+      </c>
+      <c r="J28" s="8">
+        <v>3.74</v>
+      </c>
+      <c r="K28" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="23">
+        <v>-43.1</v>
+      </c>
+      <c r="G29" s="23">
+        <v>-45.07</v>
+      </c>
+      <c r="H29" s="23">
+        <v>0.63</v>
+      </c>
+      <c r="I29" s="23">
+        <v>1.97</v>
+      </c>
+      <c r="J29" s="8">
+        <v>3.11</v>
+      </c>
+      <c r="K29" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F30" s="23">
+        <v>-45.07</v>
+      </c>
+      <c r="G30" s="23">
+        <v>-49.11</v>
+      </c>
+      <c r="H30" s="23">
+        <v>0.62</v>
+      </c>
+      <c r="I30" s="23">
+        <v>4.04</v>
+      </c>
+      <c r="J30" s="15">
+        <v>6.55</v>
+      </c>
+      <c r="K30" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="23">
+        <v>-49.11</v>
+      </c>
+      <c r="G31" s="23">
+        <v>-51.23</v>
+      </c>
+      <c r="H31" s="23">
+        <v>0.43</v>
+      </c>
+      <c r="I31" s="23">
+        <v>2.12</v>
+      </c>
+      <c r="J31" s="8">
+        <v>4.89</v>
+      </c>
+      <c r="K31" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="F32" s="23">
+        <v>-51.23</v>
+      </c>
+      <c r="G32" s="23">
+        <v>-53.2</v>
+      </c>
+      <c r="H32" s="23">
         <v>0.3</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I32" s="23">
+        <v>1.97</v>
+      </c>
+      <c r="J32" s="15">
+        <v>6.57</v>
+      </c>
+      <c r="K32" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="23">
+        <v>-53.2</v>
+      </c>
+      <c r="G33" s="23">
+        <v>-55.19</v>
+      </c>
+      <c r="H33" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="I33" s="23">
+        <v>1.99</v>
+      </c>
+      <c r="J33" s="8">
+        <v>2.65</v>
+      </c>
+      <c r="K33" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="23">
+        <v>-55.19</v>
+      </c>
+      <c r="G34" s="23">
+        <v>-57.22</v>
+      </c>
+      <c r="H34" s="23">
+        <v>0.67</v>
+      </c>
+      <c r="I34" s="23">
+        <v>2.03</v>
+      </c>
+      <c r="J34" s="8">
+        <v>3.05</v>
+      </c>
+      <c r="K34" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" s="23">
+        <v>-57.22</v>
+      </c>
+      <c r="G35" s="23">
+        <v>-59.35</v>
+      </c>
+      <c r="H35" s="23">
+        <v>0.62</v>
+      </c>
+      <c r="I35" s="23">
         <v>2.13</v>
       </c>
-      <c r="J26" s="9">
-        <v>7.1</v>
-      </c>
-      <c r="K26" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" s="19">
-        <v>-38.95</v>
-      </c>
-      <c r="G27" s="19">
-        <v>-41.12</v>
-      </c>
-      <c r="H27" s="19">
-        <v>0.7</v>
-      </c>
-      <c r="I27" s="19">
-        <v>2.17</v>
-      </c>
-      <c r="J27" s="8">
-        <v>3.1</v>
-      </c>
-      <c r="K27" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="19">
-        <v>-41.12</v>
-      </c>
-      <c r="G28" s="19">
-        <v>-43.25</v>
-      </c>
-      <c r="H28" s="19">
-        <v>0.48</v>
-      </c>
-      <c r="I28" s="19">
-        <v>2.13</v>
-      </c>
-      <c r="J28" s="8">
-        <v>4.41</v>
-      </c>
-      <c r="K28" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="19">
-        <v>-43.25</v>
-      </c>
-      <c r="G29" s="19">
-        <v>-45.36</v>
-      </c>
-      <c r="H29" s="19">
-        <v>1.13</v>
-      </c>
-      <c r="I29" s="19">
-        <v>2.11</v>
-      </c>
-      <c r="J29" s="8">
-        <v>1.86</v>
-      </c>
-      <c r="K29" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="19">
-        <v>-45.36</v>
-      </c>
-      <c r="G30" s="19">
-        <v>-47.17</v>
-      </c>
-      <c r="H30" s="19">
-        <v>0.45</v>
-      </c>
-      <c r="I30" s="19">
-        <v>1.81</v>
-      </c>
-      <c r="J30" s="8">
-        <v>4.02</v>
-      </c>
-      <c r="K30" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F31" s="19">
-        <v>-47.17</v>
-      </c>
-      <c r="G31" s="19">
-        <v>-49.54</v>
-      </c>
-      <c r="H31" s="19">
-        <v>1.13</v>
-      </c>
-      <c r="I31" s="19">
-        <v>2.37</v>
-      </c>
-      <c r="J31" s="8">
-        <v>2.09</v>
-      </c>
-      <c r="K31" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" s="19">
-        <v>-49.54</v>
-      </c>
-      <c r="G32" s="19">
-        <v>-51.68</v>
-      </c>
-      <c r="H32" s="19">
-        <v>0.45</v>
-      </c>
-      <c r="I32" s="19">
-        <v>2.14</v>
-      </c>
-      <c r="J32" s="8">
-        <v>4.76</v>
-      </c>
-      <c r="K32" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="F33" s="19">
-        <v>-51.68</v>
-      </c>
-      <c r="G33" s="19">
-        <v>-53.57</v>
-      </c>
-      <c r="H33" s="19">
-        <v>0.68</v>
-      </c>
-      <c r="I33" s="19">
-        <v>1.89</v>
-      </c>
-      <c r="J33" s="8">
-        <v>2.77</v>
-      </c>
-      <c r="K33" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="19">
-        <v>-53.57</v>
-      </c>
-      <c r="G34" s="19">
-        <v>-55.32</v>
-      </c>
-      <c r="H34" s="19">
-        <v>0.65</v>
-      </c>
-      <c r="I34" s="19">
-        <v>1.75</v>
-      </c>
-      <c r="J34" s="8">
-        <v>2.69</v>
-      </c>
-      <c r="K34" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" s="19">
-        <v>-55.32</v>
-      </c>
-      <c r="G35" s="19">
-        <v>-57.13</v>
-      </c>
-      <c r="H35" s="19">
-        <v>0.65</v>
-      </c>
-      <c r="I35" s="19">
-        <v>1.81</v>
-      </c>
       <c r="J35" s="8">
-        <v>2.78</v>
-      </c>
-      <c r="K35" s="20" t="s">
-        <v>30</v>
+        <v>3.45</v>
+      </c>
+      <c r="K35" s="24" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F36" s="19">
-        <v>-57.13</v>
-      </c>
-      <c r="G36" s="19">
-        <v>-59.27</v>
-      </c>
-      <c r="H36" s="19">
-        <v>0.7</v>
-      </c>
-      <c r="I36" s="19">
-        <v>2.14</v>
+      <c r="A36" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F36" s="23">
+        <v>-59.35</v>
+      </c>
+      <c r="G36" s="23">
+        <v>-61.2</v>
+      </c>
+      <c r="H36" s="23">
+        <v>0.47</v>
+      </c>
+      <c r="I36" s="23">
+        <v>1.85</v>
       </c>
       <c r="J36" s="8">
-        <v>3.06</v>
-      </c>
-      <c r="K36" s="20" t="s">
-        <v>30</v>
+        <v>3.96</v>
+      </c>
+      <c r="K36" s="24" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" s="19">
-        <v>-59.27</v>
-      </c>
-      <c r="G37" s="19">
-        <v>-61.05</v>
-      </c>
-      <c r="H37" s="19">
-        <v>0.75</v>
-      </c>
-      <c r="I37" s="19">
-        <v>1.78</v>
+      <c r="A37" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="23">
+        <v>-61.2</v>
+      </c>
+      <c r="G37" s="23">
+        <v>-63</v>
+      </c>
+      <c r="H37" s="23">
+        <v>0.5</v>
+      </c>
+      <c r="I37" s="23">
+        <v>1.8</v>
       </c>
       <c r="J37" s="8">
-        <v>2.37</v>
-      </c>
-      <c r="K37" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F38" s="19">
-        <v>-61.05</v>
-      </c>
-      <c r="G38" s="19">
-        <v>-63.05</v>
-      </c>
-      <c r="H38" s="19">
-        <v>0.55</v>
-      </c>
-      <c r="I38" s="19">
-        <v>2</v>
-      </c>
-      <c r="J38" s="8">
-        <v>3.64</v>
-      </c>
-      <c r="K38" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-    </row>
+        <v>3.6</v>
+      </c>
+      <c r="K37" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2191,7 +2193,6 @@
     <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="B1:K1"/>
@@ -2202,7 +2203,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2212,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2225,31 +2226,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2263,80 +2264,80 @@
         <v>27</v>
       </c>
       <c r="D2" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-9.52</v>
+        <v>-6.72</v>
       </c>
       <c r="F2" s="5">
-        <v>-16.7</v>
+        <v>-8.81</v>
       </c>
       <c r="G2" s="5">
-        <v>1.87</v>
+        <v>0.45</v>
       </c>
       <c r="H2" s="5">
-        <v>7.18</v>
+        <v>2.09</v>
       </c>
       <c r="I2" s="8">
-        <v>3.85</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="9">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9">
+        <v>-8.81</v>
+      </c>
+      <c r="F3" s="9">
+        <v>-14.1</v>
+      </c>
+      <c r="G3" s="9">
+        <v>1.53</v>
+      </c>
+      <c r="H3" s="9">
+        <v>5.29</v>
+      </c>
+      <c r="I3" s="8">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="10">
-        <v>4</v>
-      </c>
-      <c r="E3" s="10">
-        <v>-16.7</v>
-      </c>
-      <c r="F3" s="10">
-        <v>-24.6</v>
-      </c>
-      <c r="G3" s="10">
-        <v>1.35</v>
-      </c>
-      <c r="H3" s="10">
-        <v>7.9</v>
-      </c>
-      <c r="I3" s="9">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="13">
-        <v>2</v>
-      </c>
-      <c r="E4" s="13">
-        <v>-24.6</v>
-      </c>
-      <c r="F4" s="13">
-        <v>-28.7</v>
-      </c>
-      <c r="G4" s="13">
-        <v>0.78</v>
-      </c>
-      <c r="H4" s="13">
-        <v>4.1</v>
-      </c>
-      <c r="I4" s="9">
-        <v>5.23</v>
+      <c r="D4" s="12">
+        <v>8</v>
+      </c>
+      <c r="E4" s="12">
+        <v>-14.1</v>
+      </c>
+      <c r="F4" s="12">
+        <v>-31.01</v>
+      </c>
+      <c r="G4" s="12">
+        <v>2.58</v>
+      </c>
+      <c r="H4" s="12">
+        <v>16.91</v>
+      </c>
+      <c r="I4" s="15">
+        <v>6.55</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2350,22 +2351,22 @@
         <v>47</v>
       </c>
       <c r="D5" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-28.7</v>
+        <v>-31.01</v>
       </c>
       <c r="F5" s="16">
-        <v>-34.71</v>
+        <v>-33.12</v>
       </c>
       <c r="G5" s="16">
-        <v>1.33</v>
+        <v>0.4</v>
       </c>
       <c r="H5" s="16">
-        <v>6.01</v>
-      </c>
-      <c r="I5" s="8">
-        <v>4.51</v>
+        <v>2.11</v>
+      </c>
+      <c r="I5" s="15">
+        <v>5.27</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2376,54 +2377,83 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D6" s="19">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E6" s="19">
-        <v>-34.71</v>
+        <v>-33.12</v>
       </c>
       <c r="F6" s="19">
-        <v>-63.05</v>
+        <v>-37.06</v>
       </c>
       <c r="G6" s="19">
-        <v>9.03</v>
+        <v>16.18</v>
       </c>
       <c r="H6" s="19">
-        <v>28.34</v>
-      </c>
-      <c r="I6" s="8">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>30</v>
+        <v>3.94</v>
+      </c>
+      <c r="I6" s="22">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="23">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="24">
-        <v>28</v>
-      </c>
-      <c r="E7" s="24">
-        <v>-9.52</v>
-      </c>
-      <c r="F7" s="24">
-        <v>-63.05</v>
-      </c>
-      <c r="G7" s="24">
-        <v>14.37</v>
-      </c>
-      <c r="H7" s="24">
-        <v>53.53</v>
-      </c>
-      <c r="I7" s="24">
-        <v>3.73</v>
+        <v>54</v>
+      </c>
+      <c r="D7" s="23">
+        <v>12</v>
+      </c>
+      <c r="E7" s="23">
+        <v>-37.06</v>
+      </c>
+      <c r="F7" s="23">
+        <v>-63</v>
+      </c>
+      <c r="G7" s="23">
+        <v>6.88</v>
+      </c>
+      <c r="H7" s="23">
+        <v>25.94</v>
+      </c>
+      <c r="I7" s="8">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="28">
+        <v>27</v>
+      </c>
+      <c r="E8" s="28">
+        <v>-6.72</v>
+      </c>
+      <c r="F8" s="28">
+        <v>-63</v>
+      </c>
+      <c r="G8" s="28">
+        <v>28.03</v>
+      </c>
+      <c r="H8" s="28">
+        <v>56.28</v>
+      </c>
+      <c r="I8" s="28">
+        <v>2.01</v>
       </c>
     </row>
   </sheetData>
